--- a/master_data_36_inch.xlsx
+++ b/master_data_36_inch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mo/Developer/tailor-tally/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26B5D98-2CD2-124C-8540-2206ABD0B47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BAF696B-8E7E-504D-8B09-C5CC6D8DD7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30440" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1523,7 +1523,7 @@
         <v>36</v>
       </c>
       <c r="F37">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="G37" t="s">
         <v>10</v>
@@ -1569,7 +1569,7 @@
         <v>36</v>
       </c>
       <c r="F39">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="G39" t="s">
         <v>10</v>
@@ -1592,7 +1592,7 @@
         <v>36</v>
       </c>
       <c r="F40">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="G40" t="s">
         <v>10</v>
